--- a/data/trans_orig/IP07_C15_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C15_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han producido situaciones de cyberbulling fuera de su colegio en 2023 (tasa de respuesta: 92,89%)</t>
+          <t>Menores según si se han producido situaciones de cyberbulling fuera de su colegio/instituto en 2023 (tasa de respuesta: 92,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2604</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8363</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>53,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2848</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2604</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7932</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>18,47%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8637</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>51,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2848</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12927</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7168</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15531</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,23%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>46,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10724</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12569</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7485</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15417</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>81,53%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>48,55%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>32</t>
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>25138</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17629</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26141</t>
+          <t>27742</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15531</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15531</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15531</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>10724</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10724</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10724</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>26141</t>
+          <t>27742</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26141</t>
+          <t>27742</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26141</t>
+          <t>27742</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19252</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12615</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27433</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>17752</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9328</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>26230</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20469</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13397</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29467</t>
+          <t>24450</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>38221</t>
+          <t>37278</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26319</t>
+          <t>27505</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51176</t>
+          <t>48537</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>168081</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>159900</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>174718</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,27%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>134208</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>125730</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>142632</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>88,32%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>169419</t>
+          <t>117050</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160421</t>
+          <t>110627</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176491</t>
+          <t>124171</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>303627</t>
+          <t>285132</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>290672</t>
+          <t>273873</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315529</t>
+          <t>294905</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>187333</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>187333</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>187333</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>151960</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>151960</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>151960</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>189888</t>
+          <t>135077</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>189888</t>
+          <t>135077</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>189888</t>
+          <t>135077</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341848</t>
+          <t>322410</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341848</t>
+          <t>322410</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341848</t>
+          <t>322410</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4609</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9655</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3507</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1092</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8101</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8564</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15427</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>40908</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>35862</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43686</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,87%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>32604</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>28010</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>35019</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>90,29%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40021</t>
+          <t>34196</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34670</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43262</t>
+          <t>36879</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>72624</t>
+          <t>75104</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>65761</t>
+          <t>68359</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76527</t>
+          <t>79296</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>45517</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45517</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>45517</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>36111</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>36111</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>36111</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45078</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45078</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45078</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>81188</t>
+          <t>83631</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81188</t>
+          <t>83631</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81188</t>
+          <t>83631</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26465</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18627</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>37449</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>21260</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11854</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>30319</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28374</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>15458</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40210</t>
+          <t>30076</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>49633</t>
+          <t>48409</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36702</t>
+          <t>37331</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63756</t>
+          <t>60644</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>221917</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>210933</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>229755</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,92%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>177535</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>168476</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>186941</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>89,31%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,75%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>222009</t>
+          <t>163457</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>210173</t>
+          <t>155325</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>231171</t>
+          <t>169943</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>399545</t>
+          <t>385374</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>385422</t>
+          <t>373139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>412476</t>
+          <t>396452</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>248382</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>248382</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>248382</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>198795</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>198795</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>198795</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>250383</t>
+          <t>185401</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>250383</t>
+          <t>185401</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>250383</t>
+          <t>185401</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>449178</t>
+          <t>433783</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>449178</t>
+          <t>433783</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>449178</t>
+          <t>433783</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
